--- a/feedback_forms/004_thesis_defense_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/004_thesis_defense_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>thesis_defense_feedback_form_first_page</t>
+          <t>background_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Background Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page_section_1</t>
+          <t>reviewer_background</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>Reviewer's Background</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_page_section_1_question_1</t>
+          <t>evaluation_criteria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>Evaluation Criteria</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page_section_1_question_2</t>
+          <t>relevance_and_impact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>Relevance and Impact</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page_section_2</t>
+          <t>originality_and_contribution</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>Originality and Contribution</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page_section_2_question_1</t>
+          <t>research_design_and_methodology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>Research Design and Methodology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page_section_2_question_2</t>
+          <t>results_and_discussion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>Results and Discussion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page_section_3</t>
+          <t>overall_evaluation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>section_3</t>
+          <t>Overall Evaluation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page_section_3_question_1</t>
+          <t>suggestions_for_improvement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>Suggestions for Improvement</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_page_section_3_question_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>second_page_section_1</t>
+          <t>reviewer_background_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>Reviewer Background 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>second_page_section_1_question_1</t>
+          <t>reviewer_contact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>Reviewer's Contact Information</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>second_page_section_1_question_2</t>
+          <t>reviewer_signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>Reviewer's Digital Signature</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>second_page_section_2</t>
+          <t>reviewer_declaration</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>Conflicts of Interest Declaration</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,225 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>second_page_section_2_question_1</t>
+          <t>final_submission</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>Final Submission</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>second_page_section_2_question_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question_2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>second_page_section_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>section_3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>second_page_section_3_question_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>question_1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>second_page_section_3_question_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>question_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>second_page_section_3_question_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>question_3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>reviewer_input</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>reviewer_input</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +919,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>reviewer_input_choices</t>
+          <t>evaluation_criteria_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'reviewer_input_1',_'label':_'reviewer_input_1',_'value':_1}</t>
+          <t>content_and_structure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'reviewer_input_1', 'label': 'reviewer_input_1', 'value': 1}</t>
+          <t>Content and Structure</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>reviewer_input_choices</t>
+          <t>evaluation_criteria_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'reviewer_input_2',_'label':_'reviewer_input_2',_'value':_2}</t>
+          <t>methodology_and_method</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'reviewer_input_2', 'label': 'reviewer_input_2', 'value': 2}</t>
+          <t>Methodology and Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>evaluation_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>results_and_discussion</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Results and Discussion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>evaluation_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>overall_impression</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Overall Impression</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>overall_evaluation_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>overall_evaluation_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>overall_evaluation_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rating_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rating_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rating_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rating_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rating_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
